--- a/stories/arbres/TREE-AUT-010.xlsx
+++ b/stories/arbres/TREE-AUT-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec maman, sur le chemin de l'école. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo écoute maman. Hugo entend les mots : manteau, sortir, rentrer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2545,6 +2598,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2709,6 +2767,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2934,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3033,6 +3101,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3195,6 +3268,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3357,6 +3435,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3519,6 +3602,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3681,6 +3769,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3873,6 +3966,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4037,6 +4135,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4199,6 +4302,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4361,6 +4469,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4523,6 +4636,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4685,6 +4803,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4847,6 +4970,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5009,6 +5137,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5201,6 +5334,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5503,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5527,6 +5670,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5689,6 +5837,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5851,6 +6004,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6013,6 +6171,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6175,6 +6338,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6199,7 +6367,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6337,6 +6505,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6517,6 +6691,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -6685,6 +6864,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6875,6 +7059,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7037,6 +7226,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7229,6 +7423,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7393,6 +7592,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7555,6 +7759,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7717,6 +7926,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7879,6 +8093,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8041,6 +8260,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8203,6 +8427,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8365,6 +8594,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8557,6 +8791,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8721,6 +8960,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8883,6 +9127,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9045,6 +9294,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9207,6 +9461,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9369,6 +9628,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9531,6 +9795,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9693,6 +9962,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9885,6 +10159,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10049,6 +10328,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10211,6 +10495,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10373,6 +10662,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10535,6 +10829,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10697,6 +10996,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10859,6 +11163,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10883,7 +11192,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11021,6 +11330,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11201,6 +11516,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -11369,6 +11689,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11559,6 +11884,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11721,6 +12051,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11913,6 +12248,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12077,6 +12417,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12239,6 +12584,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12401,6 +12751,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12563,6 +12918,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12725,6 +13085,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12887,6 +13252,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13049,6 +13419,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13241,6 +13616,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13405,6 +13785,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13567,6 +13952,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13729,6 +14119,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13891,6 +14286,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14053,6 +14453,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14215,6 +14620,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14377,6 +14787,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14569,6 +14984,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14733,6 +15153,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14895,6 +15320,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15057,6 +15487,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15219,6 +15654,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15381,6 +15821,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15543,6 +15988,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15561,7 +16011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15634,6 +16084,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-010.xlsx
+++ b/stories/arbres/TREE-AUT-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est avec maman, sur le chemin de l'école. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo écoute maman. Hugo entend les mots : manteau, sortir, rentrer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Hugo a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2605,6 +2617,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2772,6 +2785,7 @@
           <t>narrateur|Hugo rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2939,6 +2953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3106,6 +3121,7 @@
           <t>narrateur|Hugo rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3273,6 +3289,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3440,6 +3457,7 @@
           <t>narrateur|Hugo rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3607,6 +3625,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3774,6 +3793,7 @@
           <t>narrateur|Hugo a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3973,6 +3993,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4140,6 +4161,7 @@
           <t>narrateur|Hugo rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4307,6 +4329,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4474,6 +4497,7 @@
           <t>narrateur|Hugo rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4641,6 +4665,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4808,6 +4833,7 @@
           <t>narrateur|Hugo rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4975,6 +5001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5142,6 +5169,7 @@
           <t>narrateur|Hugo a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5341,6 +5369,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5508,6 +5537,7 @@
           <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5675,6 +5705,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5842,6 +5873,7 @@
           <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6009,6 +6041,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6176,6 +6209,7 @@
           <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6343,6 +6377,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6511,6 +6546,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6698,6 +6734,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6869,6 +6906,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7064,6 +7102,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7231,6 +7270,7 @@
           <t>narrateur|Hugo a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7430,6 +7470,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7597,6 +7638,7 @@
           <t>narrateur|Hugo rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7764,6 +7806,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7931,6 +7974,7 @@
           <t>narrateur|Hugo rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8098,6 +8142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8265,6 +8310,7 @@
           <t>narrateur|Hugo rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8432,6 +8478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8599,6 +8646,7 @@
           <t>narrateur|Hugo a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8798,6 +8846,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8965,6 +9014,7 @@
           <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9132,6 +9182,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9299,6 +9350,7 @@
           <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9466,6 +9518,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9633,6 +9686,7 @@
           <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9800,6 +9854,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9967,6 +10022,7 @@
           <t>narrateur|Hugo a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10166,6 +10222,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10333,6 +10390,7 @@
           <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10500,6 +10558,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10667,6 +10726,7 @@
           <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10834,6 +10894,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11001,6 +11062,7 @@
           <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11168,6 +11230,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11336,6 +11399,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11523,6 +11587,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11694,6 +11759,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11889,6 +11955,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12056,6 +12123,7 @@
           <t>narrateur|Hugo a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12255,6 +12323,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12422,6 +12491,7 @@
           <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12589,6 +12659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12756,6 +12827,7 @@
           <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12923,6 +12995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13090,6 +13163,7 @@
           <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13257,6 +13331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13424,6 +13499,7 @@
           <t>narrateur|Hugo a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13623,6 +13699,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13790,6 +13867,7 @@
           <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13957,6 +14035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14124,6 +14203,7 @@
           <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14291,6 +14371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14458,6 +14539,7 @@
           <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14625,6 +14707,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14792,6 +14875,7 @@
           <t>narrateur|Hugo a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14991,6 +15075,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15158,6 +15243,7 @@
           <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15325,6 +15411,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15492,6 +15579,7 @@
           <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15659,6 +15747,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15826,6 +15915,7 @@
           <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15993,6 +16083,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16011,7 +16102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16091,6 +16182,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16292,6 +16397,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-010.xlsx
+++ b/stories/arbres/TREE-AUT-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prendre son manteau avant de sortir — sur le chemin de l'école</t>
+          <t>Le manteau jaune de Chouchou</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La gouttière tic. Le manteau jaune attend. Chouchou le prend avant de sortir sur le chemin de l'école. En rentrant, il le raccroche.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Hugo est avec maman, sur le chemin de l'école. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo écoute maman. Hugo entend les mots : manteau, sortir, rentrer.</t>
+          <t>Dehors, la gouttière fait tic, tic, tic. Une feuille mouillée colle au seuil. L'air frais passe sous la porte. Ça sent la terre humide. Sur le crochet, un manteau jaune attend. Une goutte brille sur le capuchon. Chouchou, tu as vu le manteau ? Il est jaune, maman. Oui. Il est tout prêt. Papa noue une chaussure, lentement. On va sortir dans un moment. Le chemin de l'école est un peu frais. On va dehors, papa ? Oui. On prend le manteau avant de sortir. En ce moment, Chouchou est près de la porte. Le manteau jaune touche sa main. Tu le prends, Chouchou ? Je prends le manteau. Un bras, puis l'autre bras. Le manteau est chaud. Bravo. Tu as fait du bon travail. Quand on rentre, on le raccroche. On le raccroche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,32 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Hugo est avec maman, sur le chemin de l'école. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo écoute maman. Hugo entend les mots : manteau, sortir, rentrer.</t>
+          <t>narrateur|Dehors, la gouttière fait tic, tic, tic.
+narrateur|Une feuille mouillée colle au seuil.
+narrateur|L'air frais passe sous la porte.
+narrateur|Ça sent la terre humide.
+narrateur|Sur le crochet, un manteau jaune attend.
+narrateur|Une goutte brille sur le capuchon.
+maman|Chouchou, tu as vu le manteau ?
+enfant-m|Il est jaune, maman.
+maman|Oui.
+maman|Il est tout prêt.
+narrateur|Papa noue une chaussure, lentement.
+papa|On va sortir dans un moment.
+papa|Le chemin de l'école est un peu frais.
+enfant-m|On va dehors, papa ?
+papa|Oui.
+papa|On prend le manteau avant de sortir.
+narrateur|En ce moment, Chouchou est près de la porte.
+narrateur|Le manteau jaune touche sa main.
+maman|Tu le prends, Chouchou ?
+enfant-m|Je prends le manteau.
+narrateur|Un bras, puis l'autre bras.
+narrateur|Le manteau est chaud.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Quand on rentre, on le raccroche.
+enfant-m|On le raccroche.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1549,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On attend son tour. Je suis là. On reste ensemble.</t>
+          <t>Chouchou marche vers le bac à sable. Le manteau jaune est sur ses épaules. Le sable est un peu froid, un peu rugueux. Ça sent le pain, quelque part au loin. On a pris le manteau avant de sortir. Oui. Il est chaud. Le sable reste dans le bac. Toi, tu restes près de nous. Chouchou touche le sable du bout des doigts. Tu as encore le manteau ? Oui, maman. Bravo. On le garde pour le chemin. En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,8 +1726,21 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On attend son tour.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Chouchou marche vers le bac à sable.
+narrateur|Le manteau jaune est sur ses épaules.
+narrateur|Le sable est un peu froid, un peu rugueux.
+narrateur|Ça sent le pain, quelque part au loin.
+maman|On a pris le manteau avant de sortir.
+enfant-m|Oui.
+enfant-m|Il est chaud.
+papa|Le sable reste dans le bac.
+papa|Toi, tu restes près de nous.
+narrateur|Chouchou touche le sable du bout des doigts.
+maman|Tu as encore le manteau ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|On le garde pour le chemin.
+papa|En rentrant, on le raccroche.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1718,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Chouchou va sur le chemin. Que prend-on avant de sortir ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1928,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Chouchou va sur le chemin.
+narrateur|Que prend-on avant de sortir ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+          <t>Chouchou touche le col du manteau. Oui. On prend le manteau avant de sortir. Plus tard, c'est l'heure de rentrer. On raccroche le manteau. Je l'ai pris. Bravo. Tu as fait du bon travail. On continue le chemin ? Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2101,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+          <t>narrateur|Chouchou touche le col du manteau.
+maman|Oui.
+maman|On prend le manteau avant de sortir.
+papa|Plus tard, c'est l'heure de rentrer.
+papa|On raccroche le manteau.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|On continue le chemin ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2274,7 +2334,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Un ballon rouge attend près du bac. Il est un peu froid, un peu lisse. Le ballon, papa ! On le pose près de nous. Le manteau reste sur toi. Chouchou pousse le ballon du pied, tout doux. Tu as pris le manteau avant de sortir ? Oui, maman. Bravo. Il te tient chaud. En rentrant, on raccroche le manteau. Et le ballon, on le pose à sa place.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2414,7 +2474,18 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+          <t>narrateur|Un ballon rouge attend près du bac.
+narrateur|Il est un peu froid, un peu lisse.
+enfant-m|Le ballon, papa !
+papa|On le pose près de nous.
+papa|Le manteau reste sur toi.
+narrateur|Chouchou pousse le ballon du pied, tout doux.
+maman|Tu as pris le manteau avant de sortir ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Il te tient chaud.
+papa|En rentrant, on raccroche le manteau.
+papa|Et le ballon, on le pose à sa place.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2442,7 +2513,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2614,7 +2685,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2642,7 +2713,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc, près du bac. Le bois du banc est un peu froid. Le ballon reste à sa place. On s'assoit une minute. Le manteau me tient chaud. On l'a pris avant de sortir. Maintenant, on rentre. À la maison, Chouchou retire le manteau. Il le raccroche au crochet. Bravo. Tu as fait du bon travail. Le manteau est à sa place ? Oui, maman. Au crochet.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2782,7 +2853,20 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc, près du bac.
+narrateur|Le bois du banc est un peu froid.
+narrateur|Le ballon reste à sa place.
+maman|On s'assoit une minute.
+enfant-m|Le manteau me tient chaud.
+papa|On l'a pris avant de sortir.
+papa|Maintenant, on rentre.
+narrateur|À la maison, Chouchou retire le manteau.
+narrateur|Il le raccroche au crochet.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|Le manteau est à sa place ?
+enfant-m|Oui, maman.
+enfant-m|Au crochet.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2810,7 +2894,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le manteau est au crochet. Bravo, Chouchou. On l'avait pris avant de sortir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2950,7 +3034,10 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le manteau est au crochet.
+maman|Bravo, Chouchou.
+papa|On l'avait pris avant de sortir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2978,7 +3065,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail du chemin. Le métal est frais sous les doigts. Le ballon est resté près du bac. On continue vers l'école. Le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo, Chouchou. Plus tard, on rentre. Chouchou raccroche le manteau. Tu as raccroché le manteau ? Oui. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3118,7 +3205,19 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail du chemin.
+narrateur|Le métal est frais sous les doigts.
+narrateur|Le ballon est resté près du bac.
+papa|On continue vers l'école.
+papa|Le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo, Chouchou.
+narrateur|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau.
+maman|Tu as raccroché le manteau ?
+enfant-m|Oui.
+enfant-m|Au crochet.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3146,7 +3245,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raccroché le manteau. Bravo. C'est du bon travail. On est rentrés ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3286,7 +3385,11 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raccroché le manteau.
+papa|Bravo.
+papa|C'est du bon travail.
+maman|On est rentrés ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3314,7 +3417,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Les cases sont un peu humides. Le ballon attend près du bac. Je saute dans la case un. Tout doucement. Le manteau reste sur toi. On l'a pris avant de sortir. Une case, puis on s'arrête. C'est l'heure de rentrer. Chouchou raccroche le manteau. Bravo. Le manteau est à sa place. Tu as fini de raccrocher ? Oui, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3454,7 +3557,20 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Les cases sont un peu humides.
+narrateur|Le ballon attend près du bac.
+enfant-m|Je saute dans la case un.
+maman|Tout doucement.
+maman|Le manteau reste sur toi.
+papa|On l'a pris avant de sortir.
+narrateur|Une case, puis on s'arrête.
+maman|C'est l'heure de rentrer.
+narrateur|Chouchou raccroche le manteau.
+papa|Bravo.
+papa|Le manteau est à sa place.
+maman|Tu as fini de raccrocher ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3482,7 +3598,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai sauté une case, tout doux. Bravo. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3622,7 +3738,10 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai sauté une case, tout doux.
+maman|Bravo.
+papa|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3650,7 +3769,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+          <t>Un seau bleu est dans le sable. Le bord est un peu rêche. Le seau, maman ! Tu le remplis tout doucement. Le sable chuchote dans le seau. Le manteau reste sur tes épaules. Il est chaud, papa. On l'a pris avant de sortir. Bravo. Tu as fait du bon travail. En rentrant, on raccroche le manteau. Et le seau, on le pose.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3790,7 +3909,18 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+          <t>narrateur|Un seau bleu est dans le sable.
+narrateur|Le bord est un peu rêche.
+enfant-m|Le seau, maman !
+maman|Tu le remplis tout doucement.
+narrateur|Le sable chuchote dans le seau.
+papa|Le manteau reste sur tes épaules.
+enfant-m|Il est chaud, papa.
+papa|On l'a pris avant de sortir.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|En rentrant, on raccroche le manteau.
+enfant-m|Et le seau, on le pose.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3818,7 +3948,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3990,7 +4120,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4018,7 +4148,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc avec le seau. Le seau pose un peu de sable au pied. On pose le seau. On s'assoit. Le manteau est chaud. On l'a pris avant de sortir. L'air sent encore la terre. On rentre maintenant. Chouchou raccroche le manteau. Bravo. Tu as fait du bon travail. Le seau est à sa place aussi ? Près de la porte, maman. Et le manteau, au crochet.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4158,7 +4288,20 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc avec le seau.
+narrateur|Le seau pose un peu de sable au pied.
+maman|On pose le seau.
+maman|On s'assoit.
+enfant-m|Le manteau est chaud.
+papa|On l'a pris avant de sortir.
+narrateur|L'air sent encore la terre.
+maman|On rentre maintenant.
+narrateur|Chouchou raccroche le manteau.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Le seau est à sa place aussi ?
+enfant-m|Près de la porte, maman.
+papa|Et le manteau, au crochet.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4186,7 +4329,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau est près de la porte. Bravo, Chouchou. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4326,7 +4469,10 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le seau est près de la porte.
+papa|Bravo, Chouchou.
+maman|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4354,7 +4500,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le seau reste près du bac à sable. On va vers l'école. Le manteau reste. Je l'ai pris avant de sortir. Bravo. Il te tient chaud. Le portail fait un petit cri de fer. On le pousse tout doucement. Plus tard, on rentre. Chouchou raccroche le manteau jaune. Tu as raccroché ? Oui, maman. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4494,7 +4640,20 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le seau reste près du bac à sable.
+papa|On va vers l'école.
+papa|Le manteau reste.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo.
+maman|Il te tient chaud.
+narrateur|Le portail fait un petit cri de fer.
+papa|On le pousse tout doucement.
+narrateur|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau jaune.
+maman|Tu as raccroché ?
+enfant-m|Oui, maman.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4522,7 +4681,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail a crié un peu. Bravo. Tu as raccroché. On avait pris le manteau avant de sortir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4662,7 +4821,11 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le portail a crié un peu.
+maman|Bravo.
+maman|Tu as raccroché.
+papa|On avait pris le manteau avant de sortir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4690,7 +4853,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le seau reste au bord, sage. Case deux, tout doux. Le manteau reste sur tes épaules. On l'a pris avant de sortir. Une goutte tombe de la gouttière, encore. On rentre. On raccroche le manteau. Chouchou le met au crochet. Bravo, Chouchou. Le seau est rentré aussi ? Oui. À sa place. Le manteau aussi.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4830,7 +4993,20 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le seau reste au bord, sage.
+enfant-m|Case deux, tout doux.
+maman|Le manteau reste sur tes épaules.
+papa|On l'a pris avant de sortir.
+narrateur|Une goutte tombe de la gouttière, encore.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Chouchou le met au crochet.
+papa|Bravo, Chouchou.
+maman|Le seau est rentré aussi ?
+enfant-m|Oui.
+enfant-m|À sa place.
+papa|Le manteau aussi.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4858,7 +5034,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau est rentré. Bravo. C'est du bon travail. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4998,7 +5174,11 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le seau est rentré.
+papa|Bravo.
+papa|C'est du bon travail.
+maman|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5026,7 +5206,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+          <t>Le doudou dépasse un peu de la poche. Il sent encore la maison. Le doudou peut regarder le sable. Il est avec moi. Le manteau aussi. On l'a pris avant de sortir. Chouchou cale le doudou contre le col. Tu as encore le manteau ? Oui, maman. Bravo. En rentrant, on le raccroche. Le doudou rentre avec nous. Dans le manteau, tout au chaud.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5166,7 +5346,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+          <t>narrateur|Le doudou dépasse un peu de la poche.
+narrateur|Il sent encore la maison.
+maman|Le doudou peut regarder le sable.
+enfant-m|Il est avec moi.
+papa|Le manteau aussi.
+papa|On l'a pris avant de sortir.
+narrateur|Chouchou cale le doudou contre le col.
+maman|Tu as encore le manteau ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|En rentrant, on le raccroche.
+papa|Le doudou rentre avec nous.
+enfant-m|Dans le manteau, tout au chaud.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5194,7 +5386,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5366,7 +5558,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5394,7 +5586,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc. Le doudou est contre le col jaune. On s'assoit. Le banc est frais. Le doudou a chaud, lui. Le manteau, on l'a pris avant de sortir. Une feuille mouillée brille au sol. On rentre maintenant. Chouchou raccroche le manteau. Le doudou rentre dans la maison. Bravo. Tu as fait du bon travail. Le manteau est au crochet ? Oui, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5534,7 +5726,20 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc.
+narrateur|Le doudou est contre le col jaune.
+maman|On s'assoit.
+maman|Le banc est frais.
+enfant-m|Le doudou a chaud, lui.
+papa|Le manteau, on l'a pris avant de sortir.
+narrateur|Une feuille mouillée brille au sol.
+maman|On rentre maintenant.
+narrateur|Chouchou raccroche le manteau.
+narrateur|Le doudou rentre dans la maison.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Le manteau est au crochet ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5562,7 +5767,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou est rentré. Bravo, Chouchou. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5702,7 +5907,10 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou est rentré.
+maman|Bravo, Chouchou.
+papa|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5730,7 +5938,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le doudou regarde à travers le grillage. On avance vers l'école. Le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo, Chouchou. Le chemin sent la terre humide. Plus tard, on rentre. Chouchou raccroche le manteau. Tu as raccroché le manteau ? Oui, papa. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5870,7 +6078,19 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le doudou regarde à travers le grillage.
+papa|On avance vers l'école.
+papa|Le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo, Chouchou.
+narrateur|Le chemin sent la terre humide.
+maman|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau.
+papa|Tu as raccroché le manteau ?
+enfant-m|Oui, papa.
+enfant-m|Au crochet.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5898,7 +6118,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou a vu le portail. Bravo. On a raccroché le manteau en rentrant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6038,7 +6258,10 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou a vu le portail.
+papa|Bravo.
+maman|On a raccroché le manteau en rentrant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6066,7 +6289,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le doudou saute la case dans sa tête. Le doudou reste dans mes bras. Oui. Et le manteau reste sur toi. On l'a pris avant de sortir. Les cases sont un peu sombres, encore humides. On rentre. On raccroche le manteau. Chouchou le pose au crochet. Bravo. Le doudou est rentré aussi. Tu as fini ? Oui, maman. Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6206,7 +6429,21 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le doudou saute la case dans sa tête.
+enfant-m|Le doudou reste dans mes bras.
+maman|Oui.
+maman|Et le manteau reste sur toi.
+papa|On l'a pris avant de sortir.
+narrateur|Les cases sont un peu sombres, encore humides.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Chouchou le pose au crochet.
+papa|Bravo.
+papa|Le doudou est rentré aussi.
+maman|Tu as fini ?
+enfant-m|Oui, maman.
+papa|Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6234,7 +6471,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou a fini la marelle. Bravo. Tu as fait du bon travail. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6374,7 +6611,11 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou a fini la marelle.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6402,7 +6643,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
+          <t>Chouchou va vers le toboggan. Le manteau jaune fait un bruit de tissu. L'échelle est fraîche sous les mains. Le vent est doux, un peu humide. On a pris le manteau avant de sortir. Il me tient chaud, papa. On monte un à un. Tout doucement. Chouchou pose les pieds, un après l'autre. Le manteau reste sur toi. Oui, maman. Bravo. Tu as fait du bon travail. Quand on rentre, on le raccroche au crochet.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6542,8 +6783,20 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On montre du doigt, sans courir.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Chouchou va vers le toboggan.
+narrateur|Le manteau jaune fait un bruit de tissu.
+narrateur|L'échelle est fraîche sous les mains.
+narrateur|Le vent est doux, un peu humide.
+papa|On a pris le manteau avant de sortir.
+enfant-m|Il me tient chaud, papa.
+maman|On monte un à un.
+maman|Tout doucement.
+narrateur|Chouchou pose les pieds, un après l'autre.
+maman|Le manteau reste sur toi.
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Quand on rentre, on le raccroche au crochet.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6571,7 +6824,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Chouchou va sur le chemin. Que prend-on avant de sortir ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6731,7 +6984,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Chouchou va sur le chemin.
+narrateur|Que prend-on avant de sortir ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6759,7 +7013,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+          <t>Le tissu jaune froisse un peu. Oui. Avant de sortir, on prend le manteau. Plus tard, on va rentrer. On raccroche le manteau. Il est sur moi. Bravo, Chouchou. Tu as encore chaud ? Oui. Juste bien.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6903,7 +7157,16 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+          <t>narrateur|Le tissu jaune froisse un peu.
+papa|Oui.
+papa|Avant de sortir, on prend le manteau.
+maman|Plus tard, on va rentrer.
+maman|On raccroche le manteau.
+enfant-m|Il est sur moi.
+papa|Bravo, Chouchou.
+maman|Tu as encore chaud ?
+enfant-m|Oui.
+enfant-m|Juste bien.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -7127,7 +7390,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Le ballon repose au pied du toboggan. Il ne roule pas. Il attend. Le ballon reste en bas. Toi, tu as le manteau. Je l'ai pris avant de sortir. Bravo, Chouchou. Le tissu jaune glisse un peu sur l'échelle. On descend tout doucement. Mes pieds, un par un. En rentrant, on raccroche le manteau. Le ballon, on le reprend à sa place.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7267,7 +7530,18 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+          <t>narrateur|Le ballon repose au pied du toboggan.
+narrateur|Il ne roule pas.
+narrateur|Il attend.
+papa|Le ballon reste en bas.
+papa|Toi, tu as le manteau.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo, Chouchou.
+narrateur|Le tissu jaune glisse un peu sur l'échelle.
+maman|On descend tout doucement.
+enfant-m|Mes pieds, un par un.
+papa|En rentrant, on raccroche le manteau.
+maman|Le ballon, on le reprend à sa place.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7295,7 +7569,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7467,7 +7741,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7495,7 +7769,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc, près du toboggan. Le ballon est resté en bas de l'échelle. On s'assoit. On reprend souffle. Le manteau a glissé un peu. On le remet. On l'avait pris avant de sortir. Chouchou remet un bouton. Bravo. Maintenant, on rentre. À la maison, il raccroche le manteau. Tu as fait du bon travail. Le manteau est au crochet ? Oui, maman. Le ballon aussi est à sa place.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7635,7 +7909,21 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc, près du toboggan.
+narrateur|Le ballon est resté en bas de l'échelle.
+maman|On s'assoit.
+maman|On reprend souffle.
+enfant-m|Le manteau a glissé un peu.
+papa|On le remet.
+papa|On l'avait pris avant de sortir.
+narrateur|Chouchou remet un bouton.
+maman|Bravo.
+maman|Maintenant, on rentre.
+narrateur|À la maison, il raccroche le manteau.
+papa|Tu as fait du bon travail.
+maman|Le manteau est au crochet ?
+enfant-m|Oui, maman.
+papa|Le ballon aussi est à sa place.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7663,7 +7951,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai remis le bouton. Bravo, Chouchou. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7803,7 +8091,10 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai remis le bouton.
+papa|Bravo, Chouchou.
+maman|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7831,7 +8122,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le ballon attend au pied du toboggan. Vers l'école, le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo. Il te tient chaud. Le portail s'ouvre, tout doucement. On rentre plus tard. Chouchou raccroche alors le manteau. Bravo, Chouchou. Tu as raccroché ? Oui. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7971,7 +8262,20 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le ballon attend au pied du toboggan.
+papa|Vers l'école, le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo.
+maman|Il te tient chaud.
+narrateur|Le portail s'ouvre, tout doucement.
+maman|On rentre plus tard.
+narrateur|Chouchou raccroche alors le manteau.
+papa|Bravo, Chouchou.
+maman|Tu as raccroché ?
+enfant-m|Oui.
+enfant-m|Au crochet.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7999,7 +8303,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail s'est ouvert. Bravo. On a pris le manteau avant de sortir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8139,7 +8443,10 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le portail s'est ouvert.
+maman|Bravo.
+papa|On a pris le manteau avant de sortir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8167,7 +8474,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le ballon reste près du toboggan. Je pose le pied dans la première case. Tout doucement. Le manteau reste. On l'a pris avant de sortir. La marelle est un peu luisante. On rentre. On raccroche le manteau. Chouchou le met au crochet. Bravo. Tu as fait du bon travail. Le ballon est rentré ? À sa place, maman. Le manteau aussi.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8307,7 +8614,21 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le ballon reste près du toboggan.
+enfant-m|Je pose le pied dans la première case.
+maman|Tout doucement.
+maman|Le manteau reste.
+papa|On l'a pris avant de sortir.
+narrateur|La marelle est un peu luisante.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Chouchou le met au crochet.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Le ballon est rentré ?
+enfant-m|À sa place, maman.
+papa|Le manteau aussi.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8335,7 +8656,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon est à sa place. Bravo. C'est du bon travail. Le manteau est raccroché. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8475,7 +8796,11 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le ballon est à sa place.
+papa|Bravo.
+papa|C'est du bon travail.
+maman|Le manteau est raccroché.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8503,7 +8828,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+          <t>Un seau attend au pied de l'échelle. Il y a un peu de sable au fond. Le seau reste en bas. Je le vois, maman. Le manteau, lui, est sur toi. On l'a pris avant de sortir. Chouchou touche le capuchon. Bravo. Il te tient chaud. En rentrant, on le raccroche. Tu as fini de regarder le seau ? Oui, papa. Il attend.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8643,7 +8968,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+          <t>narrateur|Un seau attend au pied de l'échelle.
+narrateur|Il y a un peu de sable au fond.
+maman|Le seau reste en bas.
+enfant-m|Je le vois, maman.
+papa|Le manteau, lui, est sur toi.
+papa|On l'a pris avant de sortir.
+narrateur|Chouchou touche le capuchon.
+maman|Bravo.
+maman|Il te tient chaud.
+maman|En rentrant, on le raccroche.
+papa|Tu as fini de regarder le seau ?
+enfant-m|Oui, papa.
+enfant-m|Il attend.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8671,7 +9008,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8843,7 +9180,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8871,7 +9208,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc. Le seau est resté au pied de l'échelle. On s'assoit. Le bois est lisse. Le manteau me va bien. On l'a pris avant de sortir. Une goutte tombe encore de la gouttière. On rentre maintenant. Chouchou raccroche le manteau. Bravo. C'est du bon travail. Le seau est à sa place ? Oui, papa. Et le manteau, au crochet.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9011,7 +9348,20 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc.
+narrateur|Le seau est resté au pied de l'échelle.
+papa|On s'assoit.
+papa|Le bois est lisse.
+enfant-m|Le manteau me va bien.
+maman|On l'a pris avant de sortir.
+narrateur|Une goutte tombe encore de la gouttière.
+papa|On rentre maintenant.
+narrateur|Chouchou raccroche le manteau.
+maman|Bravo.
+maman|C'est du bon travail.
+papa|Le seau est à sa place ?
+enfant-m|Oui, papa.
+maman|Et le manteau, au crochet.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9039,7 +9389,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le seau est rentré. Bravo, Chouchou. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9179,7 +9529,10 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le seau est rentré.
+maman|Bravo, Chouchou.
+papa|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9207,7 +9560,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le seau reste près du toboggan. On avance. Le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo, Chouchou. Le chemin de l'école est un peu luisant. Plus tard, on rentre. Chouchou raccroche le manteau jaune. Tu as raccroché le manteau ? Oui, papa. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9347,7 +9700,18 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le seau reste près du toboggan.
+maman|On avance.
+maman|Le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+papa|Bravo, Chouchou.
+narrateur|Le chemin de l'école est un peu luisant.
+maman|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau jaune.
+papa|Tu as raccroché le manteau ?
+enfant-m|Oui, papa.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9375,7 +9739,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le chemin était luisant. Bravo. On a raccroché le manteau en rentrant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9515,7 +9879,10 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le chemin était luisant.
+papa|Bravo.
+maman|On a raccroché le manteau en rentrant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9543,7 +9910,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le seau reste en bas, sage. Je saute la case trois, tout doux. Le manteau reste avec toi. On l'a pris avant de sortir. Les cases sentent la pluie. On rentre. On raccroche le manteau. Chouchou le pose au crochet. Bravo. Le seau est rentré aussi. Tu as fini ? Oui, papa. Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9683,7 +10050,20 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le seau reste en bas, sage.
+enfant-m|Je saute la case trois, tout doux.
+papa|Le manteau reste avec toi.
+maman|On l'a pris avant de sortir.
+narrateur|Les cases sentent la pluie.
+papa|On rentre.
+papa|On raccroche le manteau.
+narrateur|Chouchou le pose au crochet.
+maman|Bravo.
+maman|Le seau est rentré aussi.
+papa|Tu as fini ?
+enfant-m|Oui, papa.
+maman|Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9711,7 +10091,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai sauté la case trois. Bravo. Tu as fait du bon travail. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9851,7 +10231,11 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai sauté la case trois.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9879,7 +10263,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+          <t>Le doudou est calé dans une manche. Il voyage sur le toboggan, tout sage. Le doudou vient, maman. Oui. Et le manteau aussi. On a pris le manteau avant de sortir. Chouchou tient la rampe. Bravo. Tu poses les pieds. En rentrant, on raccroche le manteau. Le doudou rentre aussi. Tu as encore chaud ? Oui. Le manteau est chaud.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10019,7 +10403,20 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+          <t>narrateur|Le doudou est calé dans une manche.
+narrateur|Il voyage sur le toboggan, tout sage.
+enfant-m|Le doudou vient, maman.
+maman|Oui.
+maman|Et le manteau aussi.
+papa|On a pris le manteau avant de sortir.
+narrateur|Chouchou tient la rampe.
+papa|Bravo.
+papa|Tu poses les pieds.
+maman|En rentrant, on raccroche le manteau.
+enfant-m|Le doudou rentre aussi.
+maman|Tu as encore chaud ?
+enfant-m|Oui.
+enfant-m|Le manteau est chaud.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10047,7 +10444,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10219,7 +10616,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10247,7 +10644,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc. Le doudou est encore dans la manche. On s'assoit. On parle tout bas. Le doudou a fait le toboggan. Et toi, tu avais le manteau. On l'a pris avant de sortir. On rentre maintenant. Chouchou raccroche le manteau. Le doudou retrouve le canapé. Bravo. Tu as fait du bon travail. Le manteau est au crochet ? Oui, maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10387,7 +10784,20 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc.
+narrateur|Le doudou est encore dans la manche.
+maman|On s'assoit.
+maman|On parle tout bas.
+enfant-m|Le doudou a fait le toboggan.
+papa|Et toi, tu avais le manteau.
+papa|On l'a pris avant de sortir.
+maman|On rentre maintenant.
+narrateur|Chouchou raccroche le manteau.
+narrateur|Le doudou retrouve le canapé.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Le manteau est au crochet ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10415,7 +10825,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou est sur le canapé. Bravo, Chouchou. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10555,7 +10965,10 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou est sur le canapé.
+papa|Bravo, Chouchou.
+maman|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10583,7 +10996,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le doudou regarde le chemin de l'école. On y va. Le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo, Chouchou. Une voiture passe, loin, tout bas. Plus tard, on rentre. Chouchou raccroche le manteau. Tu as raccroché ? Oui. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10723,7 +11136,19 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le doudou regarde le chemin de l'école.
+papa|On y va.
+papa|Le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo, Chouchou.
+narrateur|Une voiture passe, loin, tout bas.
+maman|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau.
+papa|Tu as raccroché ?
+enfant-m|Oui.
+enfant-m|Au crochet.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10751,7 +11176,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une voiture est passée, loin. Bravo. On a pris le manteau avant de sortir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10891,7 +11316,10 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Une voiture est passée, loin.
+maman|Bravo.
+papa|On a pris le manteau avant de sortir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10919,7 +11347,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le doudou compte les cases, tout bas. Case une, case deux. Tout doucement. Le manteau reste. On l'a pris avant de sortir. Chouchou s'arrête, rit un peu. On rentre. On raccroche le manteau. Le crochet reprend le jaune. Bravo. Le doudou est rentré. Tu as fini de raccrocher ? Oui, maman. Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11059,7 +11487,21 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le doudou compte les cases, tout bas.
+enfant-m|Case une, case deux.
+maman|Tout doucement.
+maman|Le manteau reste.
+papa|On l'a pris avant de sortir.
+narrateur|Chouchou s'arrête, rit un peu.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Le crochet reprend le jaune.
+papa|Bravo.
+papa|Le doudou est rentré.
+maman|Tu as fini de raccrocher ?
+enfant-m|Oui, maman.
+papa|Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11087,7 +11529,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou a compté les cases. Bravo. C'est du bon travail. Le manteau est raccroché. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11227,7 +11669,11 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou a compté les cases.
+papa|Bravo.
+papa|C'est du bon travail.
+maman|Le manteau est raccroché.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11255,7 +11701,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On rit un peu. Je suis là. On reste ensemble.</t>
+          <t>Chouchou va vers les balançoires. Le sol est un peu froid sous les chaussures. Une chaîne fait un petit bruit de métal. On a pris le manteau avant de sortir. Il est jaune. Il est chaud. Tu t'assois. Le manteau reste avec toi. Chouchou s'assoit. Le bois est lisse. Tu es bien assis ? Oui, maman. Bravo. On reste ensemble. En rentrant, on raccroche le manteau. Au crochet, papa.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11395,8 +11841,22 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Hugo va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Hugo se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On rit un peu.
-maman|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Chouchou va vers les balançoires.
+narrateur|Le sol est un peu froid sous les chaussures.
+narrateur|Une chaîne fait un petit bruit de métal.
+maman|On a pris le manteau avant de sortir.
+enfant-m|Il est jaune.
+enfant-m|Il est chaud.
+papa|Tu t'assois.
+papa|Le manteau reste avec toi.
+narrateur|Chouchou s'assoit.
+narrateur|Le bois est lisse.
+maman|Tu es bien assis ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|On reste ensemble.
+papa|En rentrant, on raccroche le manteau.
+enfant-m|Au crochet, papa.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11424,7 +11884,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Chouchou va sur le chemin. Que prend-on avant de sortir ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11584,7 +12044,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Chouchou va sur le chemin.
+narrateur|Que prend-on avant de sortir ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11612,7 +12073,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+          <t>Chouchou balance un tout petit peu les pieds. Oui. On prend le manteau avant de sortir. Quand c'est l'heure de rentrer, on le raccroche. Je m'en souviens. Bravo. C'est du bon travail. On reprend le chemin ensemble ? Oui, papa.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11756,7 +12217,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Hugo respire. Hugo retient : manteau, sortir, rentrer. On continue, avec maman.</t>
+          <t>narrateur|Chouchou balance un tout petit peu les pieds.
+maman|Oui.
+maman|On prend le manteau avant de sortir.
+papa|Quand c'est l'heure de rentrer, on le raccroche.
+enfant-m|Je m'en souviens.
+maman|Bravo.
+maman|C'est du bon travail.
+papa|On reprend le chemin ensemble ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11980,7 +12449,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+          <t>Le ballon est près des balançoires. Il a une petite tache d'eau. On laisse le ballon à sa place. Toi, tu as le manteau. Je l'ai pris avant de sortir. Bravo. Tu te balances tout doux. La chaîne chante un tout petit air. En rentrant, on raccroche le manteau. Le ballon rentre à sa place aussi. Près de la porte, papa ? Oui. À sa place.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12120,7 +12589,19 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tait une seconde. papa n'est pas loin.</t>
+          <t>narrateur|Le ballon est près des balançoires.
+narrateur|Il a une petite tache d'eau.
+papa|On laisse le ballon à sa place.
+papa|Toi, tu as le manteau.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo.
+maman|Tu te balances tout doux.
+narrateur|La chaîne chante un tout petit air.
+maman|En rentrant, on raccroche le manteau.
+papa|Le ballon rentre à sa place aussi.
+enfant-m|Près de la porte, papa ?
+papa|Oui.
+papa|À sa place.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12148,7 +12629,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12320,7 +12801,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12348,7 +12829,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc, près des balançoires. Le ballon a encore sa tache d'eau. On s'assoit. Les chaînes se taisent. Le manteau m'a tenu chaud. On l'a pris avant de sortir. Chouchou souffle un peu. On rentre maintenant. Il raccroche le manteau au crochet. Bravo. Tu as fait du bon travail. Le ballon est à sa place ? Oui, papa. Le manteau aussi.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12488,7 +12969,20 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc, près des balançoires.
+narrateur|Le ballon a encore sa tache d'eau.
+papa|On s'assoit.
+papa|Les chaînes se taisent.
+enfant-m|Le manteau m'a tenu chaud.
+maman|On l'a pris avant de sortir.
+narrateur|Chouchou souffle un peu.
+papa|On rentre maintenant.
+narrateur|Il raccroche le manteau au crochet.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le ballon est à sa place ?
+enfant-m|Oui, papa.
+maman|Le manteau aussi.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12516,7 +13010,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les chaînes se taisent. Bravo, Chouchou. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12656,7 +13150,10 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Les chaînes se taisent.
+maman|Bravo, Chouchou.
+papa|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12684,7 +13181,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le ballon reste près des balançoires. On va vers l'école. Le manteau reste. Je l'ai pris avant de sortir. Bravo, Chouchou. Le portail sent le fer froid. Plus tard, on rentre. Chouchou raccroche le manteau. Tu as raccroché le manteau ? Oui, papa. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12824,7 +13321,19 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le ballon reste près des balançoires.
+maman|On va vers l'école.
+maman|Le manteau reste.
+enfant-m|Je l'ai pris avant de sortir.
+papa|Bravo, Chouchou.
+narrateur|Le portail sent le fer froid.
+maman|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau.
+papa|Tu as raccroché le manteau ?
+enfant-m|Oui, papa.
+enfant-m|Au crochet.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12852,7 +13361,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail était froid. Bravo. On a raccroché le manteau en rentrant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12992,7 +13501,10 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le portail était froid.
+papa|Bravo.
+maman|On a raccroché le manteau en rentrant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -13020,7 +13532,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le ballon reste au bord. Je saute, tout petit saut. Le manteau reste sur toi. On l'a pris avant de sortir. Les cases claquent un peu sous la semelle. On rentre. On raccroche le manteau. Chouchou le met au crochet. Bravo. Tu as fait du bon travail. Le ballon est rentré ? À sa place, maman. Le manteau aussi.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13160,7 +13672,20 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le ballon reste au bord.
+enfant-m|Je saute, tout petit saut.
+maman|Le manteau reste sur toi.
+papa|On l'a pris avant de sortir.
+narrateur|Les cases claquent un peu sous la semelle.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Chouchou le met au crochet.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|Le ballon est rentré ?
+enfant-m|À sa place, maman.
+papa|Le manteau aussi.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13188,7 +13713,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai fait un tout petit saut. Bravo. Tu as fait du bon travail. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13328,7 +13853,11 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai fait un tout petit saut.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13356,7 +13885,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+          <t>Un seau est posé sous la balançoire. Il ne bouge pas. Le seau reste au sol. Je le vois, maman. Le manteau reste sur toi. On l'a pris avant de sortir. Chouchou pose les deux mains sur la chaîne. Bravo. Tu es bien assis. En rentrant, on raccroche le manteau. Tu as fini de te balancer un peu ? Encore une fois, tout doux.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13496,7 +14025,18 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On se tient la main. papa n'est pas loin.</t>
+          <t>narrateur|Un seau est posé sous la balançoire.
+narrateur|Il ne bouge pas.
+maman|Le seau reste au sol.
+enfant-m|Je le vois, maman.
+papa|Le manteau reste sur toi.
+papa|On l'a pris avant de sortir.
+narrateur|Chouchou pose les deux mains sur la chaîne.
+maman|Bravo.
+maman|Tu es bien assis.
+maman|En rentrant, on raccroche le manteau.
+papa|Tu as fini de te balancer un peu ?
+enfant-m|Encore une fois, tout doux.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13524,7 +14064,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13696,7 +14236,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13724,7 +14264,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc. Le seau est encore sous la balançoire. On s'assoit. On pose les pieds. Le manteau est un peu mouillé au bas. On l'a pris avant de sortir. C'est bien. Chouchou essuie une goutte du doigt. On rentre. On le raccroche. Le crochet reprend le manteau jaune. Bravo, Chouchou. Le seau est à sa place ? Oui, maman. Le manteau aussi.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13864,7 +14404,21 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc.
+narrateur|Le seau est encore sous la balançoire.
+maman|On s'assoit.
+maman|On pose les pieds.
+enfant-m|Le manteau est un peu mouillé au bas.
+papa|On l'a pris avant de sortir.
+papa|C'est bien.
+narrateur|Chouchou essuie une goutte du doigt.
+maman|On rentre.
+maman|On le raccroche.
+narrateur|Le crochet reprend le manteau jaune.
+papa|Bravo, Chouchou.
+maman|Le seau est à sa place ?
+enfant-m|Oui, maman.
+papa|Le manteau aussi.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13892,7 +14446,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le bas du manteau était mouillé. Bravo. Il sèche au crochet. On l'avait pris avant de sortir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14032,7 +14586,11 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le bas du manteau était mouillé.
+papa|Bravo.
+papa|Il sèche au crochet.
+maman|On l'avait pris avant de sortir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14060,7 +14618,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le seau reste sous la balançoire, un moment. On avance vers l'école. Le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo. Il te tient chaud. Le chemin luisant mène au portail. Plus tard, on rentre. Chouchou raccroche le manteau. Tu as raccroché ? Oui. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14200,7 +14758,20 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le seau reste sous la balançoire, un moment.
+papa|On avance vers l'école.
+papa|Le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo.
+maman|Il te tient chaud.
+narrateur|Le chemin luisant mène au portail.
+maman|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau.
+papa|Tu as raccroché ?
+enfant-m|Oui.
+enfant-m|Au crochet.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14228,7 +14799,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le chemin menait au portail. Bravo, Chouchou. Le manteau est raccroché. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14368,7 +14939,10 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le chemin menait au portail.
+maman|Bravo, Chouchou.
+papa|Le manteau est raccroché.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14396,7 +14970,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le seau reste au sol, sage. Dernière case, tout doux. Le manteau reste avec toi. On l'a pris avant de sortir. Chouchou s'arrête, les deux pieds ensemble. On rentre. On raccroche le manteau. Chouchou le pose au crochet. Bravo. Le seau est rentré aussi. Tu as fini ? Oui, maman. Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14536,7 +15110,20 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le seau reste au sol, sage.
+enfant-m|Dernière case, tout doux.
+maman|Le manteau reste avec toi.
+papa|On l'a pris avant de sortir.
+narrateur|Chouchou s'arrête, les deux pieds ensemble.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Chouchou le pose au crochet.
+papa|Bravo.
+papa|Le seau est rentré aussi.
+maman|Tu as fini ?
+enfant-m|Oui, maman.
+papa|Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14564,7 +15151,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mes deux pieds ensemble. Bravo. C'est du bon travail. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14704,7 +15291,11 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Mes deux pieds ensemble.
+papa|Bravo.
+papa|C'est du bon travail.
+maman|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14732,7 +15323,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hugo a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+          <t>Le doudou est sur les genoux de Chouchou. La couverture du col est douce. Le doudou se balance aussi. Tout doucement. Le manteau, on l'a pris avant de sortir. Chouchou rit un peu, tout bas. Bravo. Tu as fait du bon travail. En rentrant, on raccroche le manteau. Le doudou aussi rentre. Tu as encore le manteau ? Oui, maman. Il est jaune.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14872,7 +15463,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Hugo répète tout bas : manteau, sortir, rentrer. On range un objet. papa n'est pas loin.</t>
+          <t>narrateur|Le doudou est sur les genoux de Chouchou.
+narrateur|La couverture du col est douce.
+enfant-m|Le doudou se balance aussi.
+maman|Tout doucement.
+papa|Le manteau, on l'a pris avant de sortir.
+narrateur|Chouchou rit un peu, tout bas.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|En rentrant, on raccroche le manteau.
+enfant-m|Le doudou aussi rentre.
+maman|Tu as encore le manteau ?
+enfant-m|Oui, maman.
+enfant-m|Il est jaune.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14900,7 +15503,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15072,7 +15675,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On peut prendre le banc, le portail, ou la marelle.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15100,7 +15703,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le banc. Le doudou est encore sur ses genoux. On s'assoit. La chaîne ne chante plus. Le doudou a bien balancé. Et toi, tu avais le manteau. On l'a pris avant de sortir. On rentre maintenant. Chouchou raccroche le manteau. Le doudou retrouve le canapé. Bravo. Tu as fait du bon travail. Le manteau est au crochet ? Oui, papa.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15240,7 +15843,20 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le banc.
+narrateur|Le doudou est encore sur ses genoux.
+papa|On s'assoit.
+papa|La chaîne ne chante plus.
+enfant-m|Le doudou a bien balancé.
+maman|Et toi, tu avais le manteau.
+maman|On l'a pris avant de sortir.
+papa|On rentre maintenant.
+narrateur|Chouchou raccroche le manteau.
+narrateur|Le doudou retrouve le canapé.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le manteau est au crochet ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15268,7 +15884,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le doudou a bien balancé. Bravo. Le manteau est au crochet. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15408,7 +16024,10 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le doudou a bien balancé.
+maman|Bravo.
+papa|Le manteau est au crochet.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15436,7 +16055,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint le portail. Le doudou cache son nez dans le col. On va vers l'école. Le manteau reste sur toi. Je l'ai pris avant de sortir. Bravo, Chouchou. Un oiseau chante une fois, au-dessus du portail. Plus tard, on rentre. Chouchou raccroche le manteau. Tu as raccroché le manteau ? Oui, maman. Au crochet. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15576,7 +16195,19 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint le portail.
+narrateur|Le doudou cache son nez dans le col.
+maman|On va vers l'école.
+papa|Le manteau reste sur toi.
+enfant-m|Je l'ai pris avant de sortir.
+maman|Bravo, Chouchou.
+narrateur|Un oiseau chante une fois, au-dessus du portail.
+papa|Plus tard, on rentre.
+narrateur|Chouchou raccroche le manteau.
+maman|Tu as raccroché le manteau ?
+enfant-m|Oui, maman.
+enfant-m|Au crochet.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15604,7 +16235,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Un oiseau a chanté au portail. Bravo, Chouchou. On a raccroché le manteau en rentrant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15744,7 +16375,10 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Un oiseau a chanté au portail.
+papa|Bravo, Chouchou.
+maman|On a raccroché le manteau en rentrant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15772,7 +16406,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Hugo rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>Chouchou rejoint la marelle. Le doudou saute la dernière case, en rêve. On a fini la marelle. Tout doucement. Le manteau est resté sur toi. On l'a pris avant de sortir. Les cases sèchent un peu, maintenant. On rentre. On raccroche le manteau. Le crochet reprend le jaune. Bravo. Le doudou est rentré. Tu as fini de raccrocher ? Oui, maman. Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15912,7 +16546,21 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Hugo rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Hugo a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Hugo a entendu : manteau, sortir, rentrer. Hugo dit merci à maman. On rentre.</t>
+          <t>narrateur|Chouchou rejoint la marelle.
+narrateur|Le doudou saute la dernière case, en rêve.
+enfant-m|On a fini la marelle.
+maman|Tout doucement.
+maman|Le manteau est resté sur toi.
+papa|On l'a pris avant de sortir.
+narrateur|Les cases sèchent un peu, maintenant.
+maman|On rentre.
+maman|On raccroche le manteau.
+narrateur|Le crochet reprend le jaune.
+papa|Bravo.
+papa|Le doudou est rentré.
+maman|Tu as fini de raccrocher ?
+enfant-m|Oui, maman.
+papa|Le manteau est à sa place.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15940,7 +16588,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La marelle est finie. Bravo. Tu as fait du bon travail. Le manteau est à sa place. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16080,7 +16728,11 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|La marelle est finie.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|Le manteau est à sa place.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16102,7 +16754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16196,6 +16848,20 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
